--- a/data/Code.xlsx
+++ b/data/Code.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Работа\Штрих код\Обработка\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Мой диск\Штрих код\Обработка\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89661B35-673D-4974-8A32-C1161439E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD5AAF0-05F5-4A3F-9101-2DC83341F2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,25 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Берёза квас лайм 1.0</t>
-  </si>
-  <si>
-    <t>Берёза квас лайм 1.5</t>
-  </si>
-  <si>
-    <t>Берёза квас классик 1.0</t>
-  </si>
-  <si>
-    <t>Берёза квас имбирь 1.0</t>
-  </si>
-  <si>
-    <t>Подникольский квас 1.5</t>
-  </si>
-  <si>
-    <t>Берёза квас имбирь 1.5 Без GS</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>prefix</t>
   </si>
@@ -70,13 +63,151 @@
   </si>
   <si>
     <t>0194819008570004</t>
+  </si>
+  <si>
+    <t>0104810178009943</t>
+  </si>
+  <si>
+    <t>0104810178009936</t>
+  </si>
+  <si>
+    <t>0104810178009929</t>
+  </si>
+  <si>
+    <t>0104810178009950</t>
+  </si>
+  <si>
+    <t>0104810178005907</t>
+  </si>
+  <si>
+    <t>0104810178005891</t>
+  </si>
+  <si>
+    <t>0104810178005723</t>
+  </si>
+  <si>
+    <t>0104810178005686</t>
+  </si>
+  <si>
+    <t>0104810178009431</t>
+  </si>
+  <si>
+    <t>0104810178009400</t>
+  </si>
+  <si>
+    <t>0104810178009455</t>
+  </si>
+  <si>
+    <t>0104810178009486</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКСАС имбирь Без GS</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС КЛАССИК 1,0</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС лайт лаймом и мятой 1,0</t>
+  </si>
+  <si>
+    <t>КВАС ХЛЕБНЫЙ ПОДНИКОЛЬСКИЙ 1,5</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС с лаймом и мятой 1,0</t>
+  </si>
+  <si>
+    <t>КРЕМ-СОДА на ароматах и подсластителях 1,5</t>
+  </si>
+  <si>
+    <t>МЕДОВУХА НОЛЬ 1,0</t>
+  </si>
+  <si>
+    <t>КРЕМ-СОДА на ароматах 1,5</t>
+  </si>
+  <si>
+    <t>СИТРО ЛАЙТ 1,5</t>
+  </si>
+  <si>
+    <t>СИТРО 1,5</t>
+  </si>
+  <si>
+    <t>СЛАДОСТЬ. ПРЯНАЯ ДЫНЯ 1,0</t>
+  </si>
+  <si>
+    <t>СЛАДОСТЬ. ПРЯНЫЙ АПЕЛЬСИН 1,0</t>
+  </si>
+  <si>
+    <t>С КОФЕ АЙС АПЕЛЬСИН 0,5</t>
+  </si>
+  <si>
+    <t>С КОФЕ АЙС АМАРЕТТО 1,5</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС имбирь 1,0</t>
+  </si>
+  <si>
+    <t>0104810178009998</t>
+  </si>
+  <si>
+    <t>0104810178010017</t>
+  </si>
+  <si>
+    <t>КВАС ПОДНИКОЛЬСКИЙ 30</t>
+  </si>
+  <si>
+    <t>КВАС ПОДНИКОЛЬСКИЙ 20</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС лайт 1,0</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС лайт с имберём 1,0</t>
+  </si>
+  <si>
+    <t>0104810178005914</t>
+  </si>
+  <si>
+    <t>КВАС ХЛЕБНЫЙ ПОДНИКОЛЬСКИЙ с имберём 1,5</t>
+  </si>
+  <si>
+    <t>0104810178010024</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС лайт с имбирем 20</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС с лаймом и мятой 1,5</t>
+  </si>
+  <si>
+    <t>0104810178009967</t>
+  </si>
+  <si>
+    <t>0104810178009974</t>
+  </si>
+  <si>
+    <t>0104810178009981</t>
+  </si>
+  <si>
+    <t>МЕДОВУХА НОЛЬ 0,98</t>
+  </si>
+  <si>
+    <t>ЗБИТЕНЬ НОЛЬ 1,0</t>
+  </si>
+  <si>
+    <t>ЗБИТЕНЬ НОЛЬ 0,98</t>
+  </si>
+  <si>
+    <t>БЕРЁЗАКВАС КЛАССИК 1,5</t>
+  </si>
+  <si>
+    <t>0104810178006195</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,20 +217,41 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,15 +259,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -397,92 +584,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="B28" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A30:A32 A2:A28" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>